--- a/Readership Reports/Word List.xlsx
+++ b/Readership Reports/Word List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Readership-Word-Cloud/Readership Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Continuous-Word-Cloud/Readership Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930A0B9D-1137-AB46-A3E0-BFEF0453265F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FD42F-B476-634F-98A1-87E451AB4D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14280" yWindow="500" windowWidth="14520" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="631">
   <si>
     <t>Vancouver</t>
   </si>
@@ -1823,9 +1823,6 @@
     <t>Espirito Santo, Brazil</t>
   </si>
   <si>
-    <t>Hammond, Louisiana</t>
-  </si>
-  <si>
     <t>Boumerdes, Algeria</t>
   </si>
   <si>
@@ -1836,6 +1833,102 @@
   </si>
   <si>
     <t>Scheuer Facundo Agustin</t>
+  </si>
+  <si>
+    <t>Shoreline, WA</t>
+  </si>
+  <si>
+    <t>Birmingham, AL</t>
+  </si>
+  <si>
+    <t>Denver, PA</t>
+  </si>
+  <si>
+    <t>Keyport, NJ</t>
+  </si>
+  <si>
+    <t>Stamford, CT</t>
+  </si>
+  <si>
+    <t>Hammond, LA</t>
+  </si>
+  <si>
+    <t>Hainan, China</t>
+  </si>
+  <si>
+    <t>Yunnan, China</t>
+  </si>
+  <si>
+    <t>Guangdong, China</t>
+  </si>
+  <si>
+    <t>Sichuan, China</t>
+  </si>
+  <si>
+    <t>Gansu, China</t>
+  </si>
+  <si>
+    <t>Anhui, China</t>
+  </si>
+  <si>
+    <t>Zhejiang, China</t>
+  </si>
+  <si>
+    <t>Shandong, China</t>
+  </si>
+  <si>
+    <t>Shanxi, China</t>
+  </si>
+  <si>
+    <t>Bogota, Colombia</t>
+  </si>
+  <si>
+    <t>Venda Nova, Brazil</t>
+  </si>
+  <si>
+    <t>Faridabad, India</t>
+  </si>
+  <si>
+    <t>Lang Long Son, Vietnam</t>
+  </si>
+  <si>
+    <t>Nam Thanh, Vietnam</t>
+  </si>
+  <si>
+    <t>Haikou, China</t>
+  </si>
+  <si>
+    <t>Yen Bai, Vietnam</t>
+  </si>
+  <si>
+    <t>Yuxi, China</t>
+  </si>
+  <si>
+    <t>Yangjiang, China</t>
+  </si>
+  <si>
+    <t>Zhaoqing, China</t>
+  </si>
+  <si>
+    <t>Yibin, China</t>
+  </si>
+  <si>
+    <t>Meishan, China</t>
+  </si>
+  <si>
+    <t>Lanzhou, China</t>
+  </si>
+  <si>
+    <t>Shangluo, China</t>
+  </si>
+  <si>
+    <t>Huaibei, China</t>
+  </si>
+  <si>
+    <t>Zibo, China</t>
+  </si>
+  <si>
+    <t>Datong, China</t>
   </si>
 </sst>
 </file>
@@ -2221,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAC4019-EF2D-7E46-9CD0-5ADF4300B4E4}">
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B632"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
@@ -6990,7 +7083,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="B596" t="s">
         <v>426</v>
@@ -6998,7 +7091,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B597" t="s">
         <v>428</v>
@@ -7006,7 +7099,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B598" t="s">
         <v>430</v>
@@ -7014,7 +7107,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B599" t="s">
         <v>430</v>
@@ -7022,10 +7115,266 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B600" t="s">
         <v>427</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A601" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B601" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A602" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B602" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A603" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B603" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A604" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B604" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A605" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B605" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A606" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B606" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A607" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B607" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A608" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B608" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A609" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B609" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A610" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B610" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A611" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B611" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A612" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B612" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A613" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B613" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A614" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B614" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A615" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B615" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A616" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B616" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A617" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B617" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A618" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B618" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A619" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B619" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A620" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B620" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A621" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B621" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A622" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B622" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A623" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B623" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A624" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B624" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A625" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B625" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A626" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B626" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A627" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B627" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A628" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B628" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A629" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B629" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A630" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B630" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A631" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B631" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A632" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B632" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/Readership Reports/Word List.xlsx
+++ b/Readership Reports/Word List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Continuous-Word-Cloud/Readership Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FD42F-B476-634F-98A1-87E451AB4D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD2375-932B-F143-8734-4199966FB662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="500" windowWidth="14520" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
+    <workbookView xWindow="-14520" yWindow="22100" windowWidth="14520" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="681">
   <si>
     <t>Vancouver</t>
   </si>
@@ -1929,6 +1929,156 @@
   </si>
   <si>
     <t>Datong, China</t>
+  </si>
+  <si>
+    <t>Slidell, LA</t>
+  </si>
+  <si>
+    <t>Little Rock</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Mount Laurel, NJ</t>
+  </si>
+  <si>
+    <t>Eatontown, NJ</t>
+  </si>
+  <si>
+    <t>Piscataway, NJ</t>
+  </si>
+  <si>
+    <t>Secaucus, NJ</t>
+  </si>
+  <si>
+    <t>Scranton, PA</t>
+  </si>
+  <si>
+    <t>Ipswich, MA</t>
+  </si>
+  <si>
+    <t>Fez, Morocco</t>
+  </si>
+  <si>
+    <t>Dundee, Scotland</t>
+  </si>
+  <si>
+    <t>Midrand, South Africa</t>
+  </si>
+  <si>
+    <t>Pando, Uruguay</t>
+  </si>
+  <si>
+    <t>Mudukulattur, India</t>
+  </si>
+  <si>
+    <t>Tamil Nadu, India</t>
+  </si>
+  <si>
+    <t>Panipat, India</t>
+  </si>
+  <si>
+    <t>Haryana, India</t>
+  </si>
+  <si>
+    <t>Kota, India</t>
+  </si>
+  <si>
+    <t>Chhattisgarh, India</t>
+  </si>
+  <si>
+    <t>Lincang, China</t>
+  </si>
+  <si>
+    <t>Phu Yen, Vietnam</t>
+  </si>
+  <si>
+    <t>Hung Yen, Vietnam</t>
+  </si>
+  <si>
+    <t>Tuy Hoa, Vietnam</t>
+  </si>
+  <si>
+    <t>Phu Quoc, Vietnam</t>
+  </si>
+  <si>
+    <t>Kien Giang, Viet Nam</t>
+  </si>
+  <si>
+    <t>Can Duoc, Vietnam</t>
+  </si>
+  <si>
+    <t>Long An, Vietnam</t>
+  </si>
+  <si>
+    <t>Haiphong, Vietnam</t>
+  </si>
+  <si>
+    <t>Bijie, China</t>
+  </si>
+  <si>
+    <t>Guizhou, China</t>
+  </si>
+  <si>
+    <t>Maoming, China</t>
+  </si>
+  <si>
+    <t>Foshan, China</t>
+  </si>
+  <si>
+    <t>Qingyuan, China</t>
+  </si>
+  <si>
+    <t>Xiamen, China</t>
+  </si>
+  <si>
+    <t>Fujian, China</t>
+  </si>
+  <si>
+    <t>Ganzhou, China</t>
+  </si>
+  <si>
+    <t>Jiangxi, China</t>
+  </si>
+  <si>
+    <t>Yichun, China</t>
+  </si>
+  <si>
+    <t>Lishui, China</t>
+  </si>
+  <si>
+    <t>Huangshi, China</t>
+  </si>
+  <si>
+    <t>Hubei, China</t>
+  </si>
+  <si>
+    <t>Tongling, China</t>
+  </si>
+  <si>
+    <t>Nanjing, China</t>
+  </si>
+  <si>
+    <t>Jiangsu, China</t>
+  </si>
+  <si>
+    <t>Nantong, China</t>
+  </si>
+  <si>
+    <t>Haidong, China</t>
+  </si>
+  <si>
+    <t>Qinghai, China</t>
+  </si>
+  <si>
+    <t>Ulanqab, China</t>
+  </si>
+  <si>
+    <t>Nei Mongol, China</t>
+  </si>
+  <si>
+    <t>University Ibno Zohr Agadir</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAC4019-EF2D-7E46-9CD0-5ADF4300B4E4}">
-  <dimension ref="A1:B632"/>
+  <dimension ref="A1:B684"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
@@ -7377,6 +7527,422 @@
         <v>430</v>
       </c>
     </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A633" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B633" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A634" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B634" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A635" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B635" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A636" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B636" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A637" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B637" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A638" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B638" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A639" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B639" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A640" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B640" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A641" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B641" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A642" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B642" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A643" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B643" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A644" t="s">
+        <v>641</v>
+      </c>
+      <c r="B644" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A645" t="s">
+        <v>642</v>
+      </c>
+      <c r="B645" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A646" t="s">
+        <v>643</v>
+      </c>
+      <c r="B646" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A647" t="s">
+        <v>644</v>
+      </c>
+      <c r="B647" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A648" t="s">
+        <v>645</v>
+      </c>
+      <c r="B648" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A649" t="s">
+        <v>646</v>
+      </c>
+      <c r="B649" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A650" t="s">
+        <v>647</v>
+      </c>
+      <c r="B650" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A651" t="s">
+        <v>648</v>
+      </c>
+      <c r="B651" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A652" t="s">
+        <v>649</v>
+      </c>
+      <c r="B652" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A653" t="s">
+        <v>650</v>
+      </c>
+      <c r="B653" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A654" t="s">
+        <v>651</v>
+      </c>
+      <c r="B654" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A655" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B655" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A656" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B656" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A657" t="s">
+        <v>654</v>
+      </c>
+      <c r="B657" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A658" t="s">
+        <v>655</v>
+      </c>
+      <c r="B658" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A659" t="s">
+        <v>656</v>
+      </c>
+      <c r="B659" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A660" t="s">
+        <v>657</v>
+      </c>
+      <c r="B660" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A661" t="s">
+        <v>658</v>
+      </c>
+      <c r="B661" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A662" t="s">
+        <v>659</v>
+      </c>
+      <c r="B662" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A663" t="s">
+        <v>660</v>
+      </c>
+      <c r="B663" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A664" t="s">
+        <v>661</v>
+      </c>
+      <c r="B664" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A665" t="s">
+        <v>662</v>
+      </c>
+      <c r="B665" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A666" t="s">
+        <v>663</v>
+      </c>
+      <c r="B666" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A667" t="s">
+        <v>664</v>
+      </c>
+      <c r="B667" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A668" t="s">
+        <v>665</v>
+      </c>
+      <c r="B668" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A669" t="s">
+        <v>666</v>
+      </c>
+      <c r="B669" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A670" t="s">
+        <v>667</v>
+      </c>
+      <c r="B670" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A671" t="s">
+        <v>668</v>
+      </c>
+      <c r="B671" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A672" t="s">
+        <v>669</v>
+      </c>
+      <c r="B672" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A673" t="s">
+        <v>670</v>
+      </c>
+      <c r="B673" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A674" t="s">
+        <v>671</v>
+      </c>
+      <c r="B674" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A675" t="s">
+        <v>672</v>
+      </c>
+      <c r="B675" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A676" t="s">
+        <v>610</v>
+      </c>
+      <c r="B676" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A677" t="s">
+        <v>673</v>
+      </c>
+      <c r="B677" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A678" t="s">
+        <v>674</v>
+      </c>
+      <c r="B678" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A679" t="s">
+        <v>675</v>
+      </c>
+      <c r="B679" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A680" t="s">
+        <v>676</v>
+      </c>
+      <c r="B680" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A681" t="s">
+        <v>677</v>
+      </c>
+      <c r="B681" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A682" t="s">
+        <v>678</v>
+      </c>
+      <c r="B682" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A683" t="s">
+        <v>679</v>
+      </c>
+      <c r="B683" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A684" t="s">
+        <v>680</v>
+      </c>
+      <c r="B684" t="s">
+        <v>428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
